--- a/2026_attendees_list.xlsx
+++ b/2026_attendees_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="8_{35B32316-2A2A-48A1-8D9E-A84C4BEF1B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{753480B8-1FC9-4CA9-A5BD-6E25A5BCFA0B}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{58E1B9B6-CCFB-4B3C-BC90-368771935495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00716201-0881-491F-8E22-2F1932D54318}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="설문지 응답 시트1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'설문지 응답 시트1'!$A$1:$B$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'설문지 응답 시트1'!$A$1:$B$75</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="101">
   <si>
     <t>박현후</t>
   </si>
@@ -52,12 +52,6 @@
     <t>권민수</t>
   </si>
   <si>
-    <t>전인수</t>
-  </si>
-  <si>
-    <t>서울대학교</t>
-  </si>
-  <si>
     <t>박재흥</t>
   </si>
   <si>
@@ -169,9 +163,6 @@
     <t>김세린</t>
   </si>
   <si>
-    <t>조은진</t>
-  </si>
-  <si>
     <t>강준원</t>
   </si>
   <si>
@@ -182,9 +173,6 @@
   </si>
   <si>
     <t>김관혁</t>
-  </si>
-  <si>
-    <t>이덕행</t>
   </si>
   <si>
     <t>류민서</t>
@@ -426,6 +414,26 @@
   </si>
   <si>
     <t>김기수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임조령</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김동규</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이민경</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박경선</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>충북대학교</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -821,7 +829,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
@@ -831,15 +839,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -847,10 +855,10 @@
     </row>
     <row r="3" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -858,20 +866,20 @@
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>1</v>
@@ -879,7 +887,7 @@
     </row>
     <row r="7" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>1</v>
@@ -887,39 +895,39 @@
     </row>
     <row r="8" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>1</v>
+      <c r="A11" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>1</v>
@@ -927,7 +935,7 @@
     </row>
     <row r="13" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>1</v>
@@ -935,95 +943,95 @@
     </row>
     <row r="14" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>89</v>
+        <v>15</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>83</v>
+      <c r="A18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>88</v>
+      <c r="A19" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>88</v>
+        <v>71</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>78</v>
+        <v>26</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>1</v>
@@ -1031,82 +1039,82 @@
     </row>
     <row r="26" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>1</v>
+      <c r="A27" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>71</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>86</v>
+        <v>66</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>83</v>
+        <v>36</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>1</v>
+        <v>52</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>84</v>
+        <v>27</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1114,100 +1122,100 @@
         <v>25</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>84</v>
+        <v>16</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>1</v>
+        <v>55</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>88</v>
+        <v>58</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>1</v>
+        <v>48</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>1</v>
@@ -1215,15 +1223,15 @@
     </row>
     <row r="49" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>98</v>
+        <v>59</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>1</v>
@@ -1231,159 +1239,159 @@
     </row>
     <row r="51" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>46</v>
+        <v>57</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>97</v>
+      <c r="A53" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>85</v>
+      <c r="A54" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>90</v>
+      <c r="A55" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>87</v>
+        <v>14</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>78</v>
+        <v>42</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>42</v>
+        <v>11</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>91</v>
+        <v>32</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>86</v>
+        <v>4</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>10</v>
+        <v>64</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
-        <v>2</v>
+      <c r="A65" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>88</v>
+        <v>24</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>1</v>
+        <v>72</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>1</v>
@@ -1391,7 +1399,7 @@
     </row>
     <row r="71" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>1</v>
@@ -1399,7 +1407,7 @@
     </row>
     <row r="72" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>1</v>
@@ -1407,17 +1415,25 @@
     </row>
     <row r="73" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B75" s="1" t="s">
         <v>1</v>
       </c>
     </row>

--- a/2026_attendees_list.xlsx
+++ b/2026_attendees_list.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{58E1B9B6-CCFB-4B3C-BC90-368771935495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00716201-0881-491F-8E22-2F1932D54318}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{58E1B9B6-CCFB-4B3C-BC90-368771935495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A13E348-9B84-4A42-B54E-B1F4D7931259}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4320" yWindow="735" windowWidth="15075" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="설문지 응답 시트1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'설문지 응답 시트1'!$A$1:$B$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'설문지 응답 시트1'!$A$1:$B$74</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="99">
   <si>
     <t>박현후</t>
   </si>
@@ -41,12 +41,6 @@
   </si>
   <si>
     <t>황나영</t>
-  </si>
-  <si>
-    <t>엄정식</t>
-  </si>
-  <si>
-    <t>공군사관학교</t>
   </si>
   <si>
     <t>권민수</t>
@@ -829,7 +823,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
@@ -839,15 +833,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -855,31 +849,31 @@
     </row>
     <row r="3" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>1</v>
@@ -887,7 +881,7 @@
     </row>
     <row r="7" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>1</v>
@@ -895,23 +889,23 @@
     </row>
     <row r="8" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>1</v>
@@ -919,15 +913,15 @@
     </row>
     <row r="11" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>1</v>
@@ -935,7 +929,7 @@
     </row>
     <row r="13" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>1</v>
@@ -943,7 +937,7 @@
     </row>
     <row r="14" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>1</v>
@@ -951,15 +945,15 @@
     </row>
     <row r="15" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>1</v>
@@ -967,71 +961,71 @@
     </row>
     <row r="17" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>1</v>
@@ -1039,7 +1033,7 @@
     </row>
     <row r="26" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>1</v>
@@ -1047,15 +1041,15 @@
     </row>
     <row r="27" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>1</v>
@@ -1063,7 +1057,7 @@
     </row>
     <row r="29" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>1</v>
@@ -1071,15 +1065,15 @@
     </row>
     <row r="30" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>1</v>
@@ -1087,18 +1081,18 @@
     </row>
     <row r="32" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1111,7 +1105,7 @@
     </row>
     <row r="35" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>1</v>
@@ -1119,31 +1113,31 @@
     </row>
     <row r="36" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>1</v>
@@ -1151,39 +1145,39 @@
     </row>
     <row r="40" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>1</v>
@@ -1191,7 +1185,7 @@
     </row>
     <row r="45" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>1</v>
@@ -1199,23 +1193,23 @@
     </row>
     <row r="46" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>1</v>
@@ -1223,7 +1217,7 @@
     </row>
     <row r="49" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>1</v>
@@ -1231,90 +1225,90 @@
     </row>
     <row r="50" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>1</v>
+        <v>55</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>94</v>
+        <v>63</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>44</v>
+      <c r="A53" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>82</v>
+      <c r="A54" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>93</v>
+      <c r="A55" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>81</v>
+        <v>40</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>86</v>
+        <v>9</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>83</v>
+        <v>71</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1322,12 +1316,12 @@
         <v>30</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>1</v>
@@ -1335,23 +1329,23 @@
     </row>
     <row r="63" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>1</v>
+        <v>62</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="1" t="s">
-        <v>64</v>
+      <c r="A64" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="5" t="s">
-        <v>96</v>
+      <c r="A65" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>80</v>
@@ -1359,31 +1353,31 @@
     </row>
     <row r="66" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B67" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B67" s="4" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>84</v>
+        <v>31</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>1</v>
@@ -1391,7 +1385,7 @@
     </row>
     <row r="70" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>1</v>
@@ -1399,7 +1393,7 @@
     </row>
     <row r="71" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>1</v>
@@ -1407,7 +1401,7 @@
     </row>
     <row r="72" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>1</v>
@@ -1415,25 +1409,17 @@
     </row>
     <row r="73" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B75" s="1" t="s">
         <v>1</v>
       </c>
     </row>

--- a/2026_attendees_list.xlsx
+++ b/2026_attendees_list.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{58E1B9B6-CCFB-4B3C-BC90-368771935495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A13E348-9B84-4A42-B54E-B1F4D7931259}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{58E1B9B6-CCFB-4B3C-BC90-368771935495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D90758AE-5AD4-4AEE-B3AD-ACD423C97722}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="735" windowWidth="15075" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6915" yWindow="2535" windowWidth="17085" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="설문지 응답 시트1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'설문지 응답 시트1'!$A$1:$B$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'설문지 응답 시트1'!$A$1:$B$76</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="101">
   <si>
     <t>박현후</t>
   </si>
@@ -428,6 +428,14 @@
   </si>
   <si>
     <t>충북대학교</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전문진</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김은혁</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -823,7 +831,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
@@ -992,120 +1000,120 @@
       </c>
     </row>
     <row r="21" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>82</v>
+      <c r="A21" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>72</v>
+        <v>24</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
+      <c r="B27" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B28" s="5" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>80</v>
+        <v>34</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>1</v>
@@ -1113,79 +1121,79 @@
     </row>
     <row r="36" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>78</v>
+        <v>23</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>11</v>
+        <v>49</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>78</v>
+        <v>45</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>11</v>
+        <v>53</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>1</v>
@@ -1193,23 +1201,23 @@
     </row>
     <row r="46" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>82</v>
+        <v>19</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>1</v>
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>1</v>
@@ -1217,7 +1225,7 @@
     </row>
     <row r="49" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>1</v>
@@ -1225,103 +1233,103 @@
     </row>
     <row r="50" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>92</v>
+        <v>33</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>1</v>
+        <v>55</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="5" t="s">
+    <row r="54" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B54" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="4" t="s">
+    <row r="55" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B55" s="4" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>84</v>
+        <v>12</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>81</v>
+        <v>40</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>1</v>
@@ -1329,63 +1337,63 @@
     </row>
     <row r="63" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B64" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="5" t="s">
+    <row r="65" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B65" s="5" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>82</v>
+      <c r="A67" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>1</v>
+        <v>70</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>1</v>
@@ -1393,7 +1401,7 @@
     </row>
     <row r="71" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>1</v>
@@ -1401,7 +1409,7 @@
     </row>
     <row r="72" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>1</v>
@@ -1409,17 +1417,33 @@
     </row>
     <row r="73" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>1</v>
       </c>
     </row>

--- a/2026_attendees_list.xlsx
+++ b/2026_attendees_list.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{58E1B9B6-CCFB-4B3C-BC90-368771935495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D90758AE-5AD4-4AEE-B3AD-ACD423C97722}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{58E1B9B6-CCFB-4B3C-BC90-368771935495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6E67653-0E88-4E48-B487-46D18CA9EC79}"/>
   <bookViews>
-    <workbookView xWindow="6915" yWindow="2535" windowWidth="17085" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="75" yWindow="2115" windowWidth="17085" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="설문지 응답 시트1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'설문지 응답 시트1'!$A$1:$B$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'설문지 응답 시트1'!$A$1:$B$77</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="103">
   <si>
     <t>박현후</t>
   </si>
@@ -438,12 +438,20 @@
     <t>김은혁</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>서정준</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김기정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -514,6 +522,13 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -535,7 +550,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -561,6 +576,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -831,7 +847,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B78"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
@@ -911,33 +927,33 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+      <c r="B11" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>1</v>
@@ -945,7 +961,7 @@
     </row>
     <row r="14" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>1</v>
@@ -953,175 +969,175 @@
     </row>
     <row r="15" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>83</v>
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
+    <row r="20" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B20" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+    <row r="21" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+    <row r="22" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B22" s="5" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>72</v>
+        <v>24</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
+      <c r="B28" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B29" s="5" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>80</v>
+        <v>34</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>1</v>
@@ -1129,63 +1145,63 @@
     </row>
     <row r="37" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>1</v>
+        <v>49</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>78</v>
+        <v>14</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>11</v>
@@ -1193,31 +1209,31 @@
     </row>
     <row r="45" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>1</v>
+        <v>53</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>82</v>
+        <v>56</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>1</v>
@@ -1225,15 +1241,15 @@
     </row>
     <row r="49" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>1</v>
+        <v>46</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>1</v>
@@ -1241,15 +1257,15 @@
     </row>
     <row r="51" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>92</v>
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>1</v>
@@ -1257,119 +1273,119 @@
     </row>
     <row r="53" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="5" t="s">
+    <row r="56" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B56" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="4" t="s">
+    <row r="57" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B57" s="4" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>81</v>
+        <v>12</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>72</v>
+        <v>40</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>85</v>
+        <v>30</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>78</v>
+      <c r="A65" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>78</v>
@@ -1377,39 +1393,39 @@
     </row>
     <row r="68" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>82</v>
+      <c r="A69" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>1</v>
+        <v>70</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>1</v>
@@ -1417,7 +1433,7 @@
     </row>
     <row r="73" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>1</v>
@@ -1425,7 +1441,7 @@
     </row>
     <row r="74" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>1</v>
@@ -1433,17 +1449,33 @@
     </row>
     <row r="75" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>1</v>
       </c>
     </row>
